--- a/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1,348 +1,184 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="__tables__" sheetId="1" r:id="rId1"/>
+    <sheet name="__tables__" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="47">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>full_name</t>
-  </si>
-  <si>
-    <t>value_type</t>
-  </si>
-  <si>
-    <t>read_schema_from_file</t>
-  </si>
-  <si>
-    <t>input</t>
-  </si>
-  <si>
-    <t>index</t>
-  </si>
-  <si>
-    <t>mode</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>output</t>
-  </si>
-  <si>
-    <t>cfg.TbWeapon</t>
-  </si>
-  <si>
-    <t>Weapon</t>
-  </si>
-  <si>
-    <t>weapon.xlsx</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>map</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>武器表</t>
-  </si>
-  <si>
-    <t>cfg.TbLevel</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>level.xlsx</t>
-  </si>
-  <si>
-    <t>list</t>
-  </si>
-  <si>
-    <t>关卡表</t>
-  </si>
-  <si>
-    <t>cfg.TbItem</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>item.xlsx</t>
-  </si>
-  <si>
-    <t>道具表</t>
-  </si>
-  <si>
-    <t>cfg.TbPlayer</t>
-  </si>
-  <si>
-    <t>Player</t>
-  </si>
-  <si>
-    <t>player.xlsx</t>
-  </si>
-  <si>
-    <t>玩家属性表</t>
-  </si>
-  <si>
-    <t>cfg.TbEnemy</t>
-  </si>
-  <si>
-    <t>Enemy</t>
-  </si>
-  <si>
-    <t>Enemy@battle.xlsx</t>
-  </si>
-  <si>
-    <t>敌人属性表</t>
-  </si>
-  <si>
-    <t>cfg.TbWave</t>
-  </si>
-  <si>
-    <t>Wave</t>
-  </si>
-  <si>
-    <t>Wave@battle.xlsx</t>
-  </si>
-  <si>
-    <t>波次表</t>
-  </si>
-  <si>
-    <t>cfg.TbDrop</t>
-  </si>
-  <si>
-    <t>Drop</t>
-  </si>
-  <si>
-    <t>Drop@battle.xlsx</t>
-  </si>
-  <si>
-    <t>掉落表</t>
-  </si>
-  <si>
-    <t>cfg.TbBuff</t>
-  </si>
-  <si>
-    <t>Buff</t>
-  </si>
-  <si>
-    <t>buff.xlsx</t>
-  </si>
-  <si>
-    <t>Buff表</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="21">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -642,154 +478,154 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -843,11 +679,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1134,262 +1033,398 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="13.75" customWidth="1"/>
-    <col min="3" max="3" width="11.5" customWidth="1"/>
-    <col min="4" max="4" width="23.75" customWidth="1"/>
-    <col min="5" max="5" width="19.375" customWidth="1"/>
+    <col width="13.75" customWidth="1" min="2" max="2"/>
+    <col width="11.5" customWidth="1" min="3" max="3"/>
+    <col width="23.75" customWidth="1" min="4" max="4"/>
+    <col width="19.375" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>value_type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>read_schema_from_file</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>cfg.TbWeapon</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
       </c>
       <c r="D2" t="b">
         <v>0</v>
       </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>weapon.xlsx</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>武器表</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:11">
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>cfg.TbLevel</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
       </c>
       <c r="D3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" t="s">
-        <v>22</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>level.xlsx</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>关卡表</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:11">
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>cfg.TbItem</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
       </c>
       <c r="D4" t="b">
         <v>0</v>
       </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" t="s">
-        <v>26</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>item.xlsx</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>道具表</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>cfg.TbPlayer</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
       </c>
       <c r="D5" t="b">
         <v>0</v>
       </c>
-      <c r="E5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" t="s">
-        <v>30</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>player.xlsx</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>玩家属性表</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>cfg.TbEnemy</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
       </c>
       <c r="D6" t="b">
         <v>0</v>
       </c>
-      <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" t="s">
-        <v>34</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>enemy.xlsx</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>敌人属性表</t>
+        </is>
       </c>
     </row>
-    <row r="7" spans="1:11">
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>cfg.TbWave</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Wave</t>
+        </is>
       </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" t="s">
-        <v>38</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Wave@battle.xlsx</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>波次表</t>
+        </is>
       </c>
     </row>
-    <row r="8" spans="1:11">
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" t="s">
-        <v>40</v>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>cfg.TbDrop</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
       </c>
       <c r="D8" t="b">
         <v>0</v>
       </c>
-      <c r="E8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" t="s">
-        <v>42</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Drop@battle.xlsx</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>掉落表</t>
+        </is>
       </c>
     </row>
-    <row r="9" spans="1:11">
-      <c r="B9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" t="s">
-        <v>44</v>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>cfg.TbBuff</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
       </c>
       <c r="D9" t="b">
         <v>0</v>
       </c>
-      <c r="E9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" t="s">
-        <v>46</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>buff.xlsx</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Buff表</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.75" customWidth="1" min="2" max="2"/>
@@ -1424,6 +1424,46 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>cfg.TbPortal</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>portal.xlsx</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>传送门表</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.75" customWidth="1" min="2" max="2"/>
@@ -1464,6 +1464,46 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>cfg.TbInventoryConfig</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>InventoryConfig</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>inventory.xlsx</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>背包容量表</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.75" customWidth="1" min="2" max="2"/>
@@ -1504,6 +1504,166 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cfg.TbCamera</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Camera</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>camera.xlsx</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>相机配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>cfg.TbBallistic</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ballistic</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ballistic.xlsx</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>弹道全局配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>cfg.TbUiConfig</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>UiConfig</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ui_config.xlsx</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>UI全局配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>cfg.TbPickup</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pickup</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>pickup.xlsx</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>拾取物配置</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.75" customWidth="1" min="2" max="2"/>
@@ -1664,6 +1664,206 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>cfg.TbBuilding</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>building.xlsx</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>建筑表</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>cfg.TbProduction</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>production.xlsx</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>生产配方表</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>cfg.TbOrder</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>order.xlsx</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>订单表</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>cfg.TbSimTimeConfig</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SimTimeConfig</t>
+        </is>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>sim_time_config.xlsx</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>经营时间配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>cfg.TbCamera3D</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Camera3D</t>
+        </is>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>camera3d.xlsx</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3D摄像机配置</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.75" customWidth="1" min="2" max="2"/>
@@ -1864,6 +1864,46 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>cfg.TbLootContainer</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LootContainer</t>
+        </is>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>lootcontainer.xlsx</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>容器掉落表</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.75" customWidth="1" min="2" max="2"/>
@@ -1904,6 +1904,46 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>cfg.TbNote</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>note.xlsx</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>小纸条表</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.75" customWidth="1" min="2" max="2"/>
@@ -1944,6 +1944,86 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>cfg.TbPlayerLevel</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PlayerLevel</t>
+        </is>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>playerlevel.xlsx</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>玩家等级经验表</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>cfg.TbUnlock</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Unlock</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>unlock.xlsx</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>内容解锁表</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
